--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Biblioteche (1).xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Biblioteche (1).xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="177">
   <si>
     <r>
       <t xml:space="preserve">
@@ -1103,9 +1103,9 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">
-Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
+Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
 Se hai già provveduto a pagare l'avviso, ignora questo messaggio.
-Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio
+Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
 In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.</t>
     </r>
   </si>
@@ -1846,7 +1846,7 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">
-Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
+Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
 Se hai già provveduto a pagare l'avviso, ignora questo messaggio.
 Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
 In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.</t>
@@ -1895,141 +1895,6 @@
       </rPr>
       <t xml:space="preserve"> è disponibile per la consegna.
 La consegna avverrà secondo le modalità richieste in fase di prenotazione.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve">C’è un avviso di pagamento intestato a </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;nome&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;cognome&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> e relativo a </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;causale&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>Devi pagare:</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;00,00&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> €
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>Entro il:</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;gg/mm/aaaa&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve">
-Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
-Se hai già provveduto a pagare l'avviso, ignora questo messaggio.
-Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
-In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.</t>
     </r>
   </si>
   <si>
@@ -2213,7 +2078,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>Vedi Avviso</t>
+    <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
   </si>
   <si>
     <r>
@@ -3380,7 +3245,7 @@
         <v>124</v>
       </c>
       <c r="V5" s="34" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="W5" s="34" t="s">
         <v>114</v>
@@ -3389,13 +3254,13 @@
         <v>115</v>
       </c>
       <c r="Y5" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z5" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="Z5" s="34" t="s">
+      <c r="AA5" s="34" t="s">
         <v>127</v>
-      </c>
-      <c r="AA5" s="34" t="s">
-        <v>128</v>
       </c>
       <c r="AB5" s="34" t="s">
         <v>111</v>
@@ -3403,93 +3268,93 @@
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" s="34" t="s">
         <v>129</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="C6" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="F6" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="G6" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="H6" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="E6" s="34" t="s">
+      <c r="I6" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="J6" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="K6" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="L6" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="M6" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="N6" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="O6" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="P6" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q6" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="R6" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="F6" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="G6" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="H6" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="I6" s="34" t="s">
+      <c r="S6" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="J6" s="34" t="s">
+      <c r="T6" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="K6" s="34" t="s">
+      <c r="U6" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="V6" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="L6" s="34" t="s">
+      <c r="W6" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="M6" s="34" t="s">
+      <c r="X6" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="N6" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="O6" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="P6" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q6" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="R6" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="S6" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="T6" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="U6" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="V6" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="W6" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="X6" s="34" t="s">
-        <v>131</v>
-      </c>
       <c r="Y6" s="34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Z6" s="34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AA6" s="34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AB6" s="34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>74</v>
@@ -3575,265 +3440,265 @@
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="F8" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="G8" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="H8" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="I8" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="J8" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="K8" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="L8" s="34" t="s">
         <v>133</v>
       </c>
-      <c r="B8" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="D8" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F8" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="G8" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="H8" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="I8" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="J8" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="K8" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="L8" s="34" t="s">
-        <v>134</v>
-      </c>
       <c r="M8" s="34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N8" s="34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O8" s="34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P8" s="34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q8" s="34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="R8" s="34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="S8" s="34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T8" s="34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="U8" s="34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="V8" s="34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="W8" s="34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="X8" s="34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y8" s="34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Z8" s="34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AA8" s="34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AB8" s="34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="C9" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="D9" s="34" t="s">
         <v>137</v>
       </c>
-      <c r="D9" s="34" t="s">
+      <c r="E9" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="E9" s="34" t="s">
+      <c r="F9" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="F9" s="34" t="s">
+      <c r="G9" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="H9" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="I9" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="J9" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="G9" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="H9" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="I9" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="J9" s="34" t="s">
+      <c r="K9" s="34" t="s">
         <v>141</v>
       </c>
-      <c r="K9" s="34" t="s">
+      <c r="L9" s="34" t="s">
         <v>142</v>
       </c>
-      <c r="L9" s="34" t="s">
+      <c r="M9" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="N9" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="M9" s="34" t="s">
+      <c r="O9" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="N9" s="34" t="s">
+      <c r="P9" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q9" s="34" t="s">
         <v>144</v>
       </c>
-      <c r="O9" s="34" t="s">
-        <v>144</v>
-      </c>
-      <c r="P9" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q9" s="34" t="s">
+      <c r="R9" s="34" t="s">
         <v>145</v>
       </c>
-      <c r="R9" s="34" t="s">
+      <c r="S9" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="T9" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="U9" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="S9" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="T9" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="U9" s="34" t="s">
+      <c r="V9" s="34" t="s">
         <v>147</v>
       </c>
-      <c r="V9" s="34" t="s">
+      <c r="W9" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="X9" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="W9" s="34" t="s">
-        <v>148</v>
-      </c>
-      <c r="X9" s="34" t="s">
+      <c r="Y9" s="34" t="s">
         <v>149</v>
       </c>
-      <c r="Y9" s="34" t="s">
+      <c r="Z9" s="34" t="s">
         <v>150</v>
       </c>
-      <c r="Z9" s="34" t="s">
-        <v>151</v>
-      </c>
       <c r="AA9" s="34" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AB9" s="34" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="B10" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="C10" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="D10" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="E10" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="E10" s="34" t="s">
+      <c r="F10" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="F10" s="34" t="s">
+      <c r="G10" s="34" t="s">
         <v>157</v>
       </c>
-      <c r="G10" s="34" t="s">
+      <c r="H10" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="H10" s="34" t="s">
+      <c r="I10" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="J10" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="I10" s="34" t="s">
-        <v>155</v>
-      </c>
-      <c r="J10" s="34" t="s">
+      <c r="K10" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="L10" s="34" t="s">
         <v>160</v>
       </c>
-      <c r="K10" s="34" t="s">
-        <v>155</v>
-      </c>
-      <c r="L10" s="34" t="s">
+      <c r="M10" s="34" t="s">
         <v>161</v>
       </c>
-      <c r="M10" s="34" t="s">
+      <c r="N10" s="34" t="s">
         <v>162</v>
       </c>
-      <c r="N10" s="34" t="s">
+      <c r="O10" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="O10" s="34" t="s">
+      <c r="P10" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="P10" s="34" t="s">
+      <c r="Q10" s="34" t="s">
         <v>165</v>
       </c>
-      <c r="Q10" s="34" t="s">
+      <c r="R10" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="S10" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="T10" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="R10" s="34" t="s">
+      <c r="U10" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="V10" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="W10" s="34" t="s">
         <v>157</v>
       </c>
-      <c r="S10" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="T10" s="34" t="s">
-        <v>167</v>
-      </c>
-      <c r="U10" s="34" t="s">
+      <c r="X10" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y10" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="V10" s="34" t="s">
-        <v>157</v>
-      </c>
-      <c r="W10" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="X10" s="34" t="s">
-        <v>167</v>
-      </c>
-      <c r="Y10" s="34" t="s">
+      <c r="Z10" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="Z10" s="34" t="s">
+      <c r="AA10" s="34" t="s">
         <v>170</v>
       </c>
-      <c r="AA10" s="34" t="s">
-        <v>171</v>
-      </c>
       <c r="AB10" s="34" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>74</v>
@@ -3842,34 +3707,34 @@
         <v>74</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E11" s="34" t="s">
         <v>74</v>
       </c>
       <c r="F11" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="G11" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="G11" s="34" t="s">
+      <c r="H11" s="34" t="s">
         <v>174</v>
       </c>
-      <c r="H11" s="34" t="s">
-        <v>175</v>
-      </c>
       <c r="I11" s="34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J11" s="34" t="s">
         <v>74</v>
       </c>
       <c r="K11" s="34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L11" s="34" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M11" s="34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="N11" s="34" t="s">
         <v>74</v>
@@ -3884,25 +3749,25 @@
         <v>74</v>
       </c>
       <c r="R11" s="34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="S11" s="34" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T11" s="34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="U11" s="34" t="s">
         <v>74</v>
       </c>
       <c r="V11" s="34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="W11" s="34" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="X11" s="34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y11" s="34" t="s">
         <v>74</v>
@@ -3914,7 +3779,7 @@
         <v>74</v>
       </c>
       <c r="AB11" s="34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
